--- a/data_lake/industry/CFM/DDR.xlsx
+++ b/data_lake/industry/CFM/DDR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EC1103-CDBA-4998-995A-C4614D70D95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7256DE-CEDE-3848-A41B-53B2EB62CF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18020" yWindow="780" windowWidth="17980" windowHeight="20700" tabRatio="673" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -73,29 +73,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -133,54 +133,54 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -198,7 +198,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -398,6 +398,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -564,6 +585,27 @@
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="52">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -759,6 +801,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -925,6 +988,27 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="52">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
@@ -1120,6 +1204,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1286,6 +1391,27 @@
                   <c:v>19.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -1481,6 +1607,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1647,6 +1794,27 @@
                   <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="52">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>7.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -1842,6 +2010,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2008,6 +2197,27 @@
                   <c:v>2.9</c:v>
                 </c:pt>
                 <c:pt idx="52">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>2.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -2203,6 +2413,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2370,6 +2601,27 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2566,6 +2818,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2733,6 +3006,27 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2929,6 +3223,27 @@
                 <c:pt idx="52">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="53">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3096,6 +3411,27 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>24.4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>24.4</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>24.4</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>24.8</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4171,20 +4507,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.69921875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="11" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4207,7 +4543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -4230,7 +4566,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -4253,7 +4589,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -4276,7 +4612,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -4299,7 +4635,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -4322,7 +4658,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -4345,7 +4681,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -4368,7 +4704,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -4391,7 +4727,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -4414,7 +4750,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -4437,7 +4773,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -4460,7 +4796,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -4483,7 +4819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -4506,7 +4842,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -4529,7 +4865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -4552,7 +4888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -4575,7 +4911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -4598,7 +4934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -4621,7 +4957,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -4644,7 +4980,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -4667,7 +5003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -4690,7 +5026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -4713,7 +5049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -4736,7 +5072,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -4759,7 +5095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -4782,7 +5118,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -4805,7 +5141,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -4828,7 +5164,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -4851,7 +5187,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -4874,7 +5210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -4897,7 +5233,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -4920,7 +5256,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -4943,7 +5279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -4966,7 +5302,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -4989,7 +5325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -5012,7 +5348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -5035,7 +5371,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -5058,7 +5394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -5081,7 +5417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -5104,7 +5440,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -5127,7 +5463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -5150,7 +5486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -5173,7 +5509,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -5196,7 +5532,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -5219,7 +5555,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -5242,7 +5578,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -5265,7 +5601,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -5288,7 +5624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -5311,7 +5647,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -5334,7 +5670,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -5357,7 +5693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -5380,7 +5716,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -5403,7 +5739,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -5423,6 +5759,167 @@
         <v>70</v>
       </c>
       <c r="G54" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>40</v>
+      </c>
+      <c r="F55" s="11">
+        <v>70</v>
+      </c>
+      <c r="G55" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>40</v>
+      </c>
+      <c r="F56" s="11">
+        <v>70</v>
+      </c>
+      <c r="G56" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>40</v>
+      </c>
+      <c r="F57" s="11">
+        <v>70</v>
+      </c>
+      <c r="G57" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>40</v>
+      </c>
+      <c r="F58" s="11">
+        <v>70</v>
+      </c>
+      <c r="G58" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>40</v>
+      </c>
+      <c r="F59" s="11">
+        <v>70</v>
+      </c>
+      <c r="G59" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>40</v>
+      </c>
+      <c r="F60" s="11">
+        <v>70</v>
+      </c>
+      <c r="G60" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>40</v>
+      </c>
+      <c r="F61" s="11">
+        <v>70</v>
+      </c>
+      <c r="G61" s="11">
         <v>50</v>
       </c>
     </row>
@@ -5435,19 +5932,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5470,7 +5967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -5493,7 +5990,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -5516,7 +6013,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -5539,7 +6036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -5562,7 +6059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -5585,7 +6082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -5608,7 +6105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -5631,7 +6128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -5654,7 +6151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -5677,7 +6174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -5700,7 +6197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -5723,7 +6220,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -5746,7 +6243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -5769,7 +6266,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -5792,7 +6289,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -5815,7 +6312,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -5838,7 +6335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -5861,7 +6358,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -5884,7 +6381,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -5907,7 +6404,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -5930,7 +6427,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -5953,7 +6450,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -5976,7 +6473,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -5999,7 +6496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -6022,7 +6519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -6045,7 +6542,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -6068,7 +6565,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -6091,7 +6588,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -6114,7 +6611,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -6137,7 +6634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -6160,7 +6657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -6183,7 +6680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -6206,7 +6703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -6229,7 +6726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -6252,7 +6749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -6275,7 +6772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -6298,7 +6795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -6321,7 +6818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -6344,7 +6841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -6367,7 +6864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -6390,7 +6887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -6413,7 +6910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -6436,7 +6933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -6459,7 +6956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -6482,7 +6979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -6505,7 +7002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -6528,7 +7025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -6551,7 +7048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -6574,7 +7071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -6597,7 +7094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -6620,7 +7117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -6643,7 +7140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -6666,7 +7163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -6686,6 +7183,167 @@
         <v>16.5</v>
       </c>
       <c r="G54" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F55" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G55" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F56" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G56" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F57" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G57" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F58" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G58" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F59" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G59" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F60" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G60" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F61" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="G61" s="11">
         <v>16</v>
       </c>
     </row>
@@ -6697,19 +7355,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6732,7 +7390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -6755,7 +7413,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -6778,7 +7436,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -6801,7 +7459,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -6824,7 +7482,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -6847,7 +7505,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -6870,7 +7528,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -6893,7 +7551,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -6916,7 +7574,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -6939,7 +7597,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -6962,7 +7620,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -6985,7 +7643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -7008,7 +7666,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -7031,7 +7689,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -7054,7 +7712,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -7077,7 +7735,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -7100,7 +7758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -7123,7 +7781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -7146,7 +7804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -7169,7 +7827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -7192,7 +7850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -7215,7 +7873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -7238,7 +7896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -7261,7 +7919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -7284,7 +7942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -7307,7 +7965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -7330,7 +7988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -7353,7 +8011,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -7376,7 +8034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -7399,7 +8057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -7422,7 +8080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -7445,7 +8103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -7468,7 +8126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -7491,7 +8149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -7514,7 +8172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -7537,7 +8195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -7560,7 +8218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -7583,7 +8241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -7606,7 +8264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -7629,7 +8287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -7652,7 +8310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -7675,7 +8333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -7698,7 +8356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -7721,7 +8379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -7744,7 +8402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -7767,7 +8425,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -7790,7 +8448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -7813,7 +8471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -7836,7 +8494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -7859,7 +8517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -7882,7 +8540,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -7905,7 +8563,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -7928,7 +8586,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -7948,6 +8606,167 @@
         <v>32</v>
       </c>
       <c r="G54" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333329601</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>20</v>
+      </c>
+      <c r="F55" s="11">
+        <v>32</v>
+      </c>
+      <c r="G55" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333329401</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>20</v>
+      </c>
+      <c r="F56" s="11">
+        <v>32</v>
+      </c>
+      <c r="G56" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333329201</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>20</v>
+      </c>
+      <c r="F57" s="11">
+        <v>32</v>
+      </c>
+      <c r="G57" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333329002</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>20</v>
+      </c>
+      <c r="F58" s="11">
+        <v>32</v>
+      </c>
+      <c r="G58" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333328802</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>20</v>
+      </c>
+      <c r="F59" s="11">
+        <v>32</v>
+      </c>
+      <c r="G59" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333328602</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>20</v>
+      </c>
+      <c r="F60" s="11">
+        <v>32</v>
+      </c>
+      <c r="G60" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333328402</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>20</v>
+      </c>
+      <c r="F61" s="11">
+        <v>32</v>
+      </c>
+      <c r="G61" s="11">
         <v>22</v>
       </c>
     </row>
@@ -7959,20 +8778,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7995,7 +8814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -8018,7 +8837,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -8041,7 +8860,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -8064,7 +8883,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -8087,7 +8906,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -8110,7 +8929,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -8133,7 +8952,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -8156,7 +8975,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -8179,7 +8998,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -8202,7 +9021,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -8225,7 +9044,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -8248,7 +9067,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -8271,7 +9090,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -8294,7 +9113,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -8317,7 +9136,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -8340,7 +9159,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -8363,7 +9182,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -8386,7 +9205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -8409,7 +9228,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -8432,7 +9251,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -8455,7 +9274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -8478,7 +9297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -8501,7 +9320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -8524,7 +9343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -8547,7 +9366,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -8570,7 +9389,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -8593,7 +9412,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -8616,7 +9435,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -8639,7 +9458,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -8662,7 +9481,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -8685,7 +9504,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -8708,7 +9527,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -8731,7 +9550,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -8754,7 +9573,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -8777,7 +9596,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -8800,7 +9619,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -8823,7 +9642,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -8846,7 +9665,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -8869,7 +9688,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -8892,7 +9711,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -8915,7 +9734,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -8938,7 +9757,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -8961,7 +9780,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -8984,7 +9803,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -9007,7 +9826,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -9030,7 +9849,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -9053,7 +9872,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -9076,7 +9895,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -9099,7 +9918,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -9122,7 +9941,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -9145,7 +9964,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -9168,7 +9987,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -9191,7 +10010,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -9211,6 +10030,167 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="G54" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F55" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G55" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F56" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G56" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F57" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G57" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F58" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G58" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F59" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G59" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F60" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G60" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="F61" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G61" s="11">
         <v>7.8</v>
       </c>
     </row>
@@ -9222,20 +10202,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9258,7 +10238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -9281,7 +10261,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -9304,7 +10284,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -9327,7 +10307,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -9350,7 +10330,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -9373,7 +10353,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -9396,7 +10376,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -9419,7 +10399,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -9442,7 +10422,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -9465,7 +10445,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -9488,7 +10468,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -9511,7 +10491,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -9534,7 +10514,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -9557,7 +10537,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -9580,7 +10560,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -9603,7 +10583,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -9626,7 +10606,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -9649,7 +10629,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -9672,7 +10652,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -9695,7 +10675,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -9718,7 +10698,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -9741,7 +10721,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -9764,7 +10744,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -9787,7 +10767,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -9810,7 +10790,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -9833,7 +10813,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -9856,7 +10836,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -9879,7 +10859,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -9902,7 +10882,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -9925,7 +10905,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -9948,7 +10928,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -9971,7 +10951,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -9994,7 +10974,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -10017,7 +10997,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -10040,7 +11020,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -10063,7 +11043,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -10086,7 +11066,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -10109,7 +11089,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -10132,7 +11112,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -10155,7 +11135,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -10178,7 +11158,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -10201,7 +11181,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -10224,7 +11204,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -10247,7 +11227,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -10270,7 +11250,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -10293,7 +11273,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -10316,7 +11296,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -10339,7 +11319,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -10362,7 +11342,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -10385,7 +11365,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -10408,7 +11388,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -10431,7 +11411,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -10454,7 +11434,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -10474,6 +11454,167 @@
         <v>3.4</v>
       </c>
       <c r="G54" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F55" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G55" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F56" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G56" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F57" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G57" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F58" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G58" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F59" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G59" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F60" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G60" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="F61" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="G61" s="11">
         <v>2.9</v>
       </c>
     </row>
@@ -10485,19 +11626,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10520,7 +11661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -10543,7 +11684,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -10566,7 +11707,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -10589,7 +11730,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -10612,7 +11753,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -10635,7 +11776,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -10658,7 +11799,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -10681,7 +11822,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -10704,7 +11845,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -10727,7 +11868,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -10750,7 +11891,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -10773,7 +11914,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -10796,7 +11937,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -10819,7 +11960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -10842,7 +11983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -10865,7 +12006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -10888,7 +12029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -10911,7 +12052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -10934,7 +12075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -10957,7 +12098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -10980,7 +12121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -11003,7 +12144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -11026,7 +12167,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -11049,7 +12190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -11072,7 +12213,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -11095,7 +12236,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -11118,7 +12259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -11141,7 +12282,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -11164,7 +12305,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -11187,7 +12328,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -11210,7 +12351,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -11233,7 +12374,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -11256,7 +12397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -11279,7 +12420,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -11302,7 +12443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -11325,7 +12466,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -11348,7 +12489,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -11371,7 +12512,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -11394,7 +12535,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -11417,7 +12558,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -11440,7 +12581,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -11463,7 +12604,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -11486,7 +12627,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -11509,7 +12650,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -11532,7 +12673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -11555,7 +12696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -11578,7 +12719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -11601,7 +12742,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -11624,7 +12765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -11647,7 +12788,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -11670,7 +12811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -11693,7 +12834,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -11716,7 +12857,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -11737,6 +12878,167 @@
       </c>
       <c r="G54" s="11">
         <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>44</v>
+      </c>
+      <c r="F55" s="11">
+        <v>52</v>
+      </c>
+      <c r="G55" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>44</v>
+      </c>
+      <c r="F56" s="11">
+        <v>52</v>
+      </c>
+      <c r="G56" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>44</v>
+      </c>
+      <c r="F57" s="11">
+        <v>52</v>
+      </c>
+      <c r="G57" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>44</v>
+      </c>
+      <c r="F58" s="11">
+        <v>52</v>
+      </c>
+      <c r="G58" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>51</v>
+      </c>
+      <c r="F59" s="11">
+        <v>59</v>
+      </c>
+      <c r="G59" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>51</v>
+      </c>
+      <c r="F60" s="11">
+        <v>59</v>
+      </c>
+      <c r="G60" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>51</v>
+      </c>
+      <c r="F61" s="11">
+        <v>59</v>
+      </c>
+      <c r="G61" s="11">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -11747,19 +13049,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11782,7 +13084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -11805,7 +13107,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -11828,7 +13130,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -11851,7 +13153,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -11874,7 +13176,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -11897,7 +13199,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -11920,7 +13222,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -11943,7 +13245,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -11966,7 +13268,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -11989,7 +13291,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -12012,7 +13314,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -12035,7 +13337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -12058,7 +13360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -12081,7 +13383,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -12104,7 +13406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -12127,7 +13429,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -12150,7 +13452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -12173,7 +13475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -12196,7 +13498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -12219,7 +13521,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -12242,7 +13544,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -12265,7 +13567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -12288,7 +13590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -12311,7 +13613,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -12334,7 +13636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -12357,7 +13659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -12380,7 +13682,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -12403,7 +13705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -12426,7 +13728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -12449,7 +13751,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -12472,7 +13774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -12495,7 +13797,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -12518,7 +13820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -12541,7 +13843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -12564,7 +13866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -12587,7 +13889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -12610,7 +13912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -12633,7 +13935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -12656,7 +13958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -12679,7 +13981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -12702,7 +14004,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -12725,7 +14027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -12748,7 +14050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -12771,7 +14073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -12794,7 +14096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -12817,7 +14119,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -12840,7 +14142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -12863,7 +14165,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -12886,7 +14188,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -12909,7 +14211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -12932,7 +14234,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -12955,7 +14257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -12978,7 +14280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -12999,6 +14301,167 @@
       </c>
       <c r="G54" s="11">
         <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="F55" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="G55" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="F56" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="G56" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="F57" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="G57" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="F58" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="G58" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>42</v>
+      </c>
+      <c r="F59" s="11">
+        <v>46</v>
+      </c>
+      <c r="G59" s="11">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>43</v>
+      </c>
+      <c r="F60" s="11">
+        <v>47</v>
+      </c>
+      <c r="G60" s="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>43</v>
+      </c>
+      <c r="F61" s="11">
+        <v>47</v>
+      </c>
+      <c r="G61" s="11">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -13009,20 +14472,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13045,7 +14508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45860</v>
       </c>
@@ -13068,7 +14531,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45867</v>
       </c>
@@ -13091,7 +14554,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -13114,7 +14577,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45881</v>
       </c>
@@ -13137,7 +14600,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45888</v>
       </c>
@@ -13160,7 +14623,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45895</v>
       </c>
@@ -13183,7 +14646,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>45902</v>
       </c>
@@ -13206,7 +14669,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>45909</v>
       </c>
@@ -13229,7 +14692,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>45916</v>
       </c>
@@ -13252,7 +14715,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>45923</v>
       </c>
@@ -13275,7 +14738,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>45930</v>
       </c>
@@ -13298,7 +14761,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>45944</v>
       </c>
@@ -13321,7 +14784,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>45951</v>
       </c>
@@ -13344,7 +14807,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>45958</v>
       </c>
@@ -13367,7 +14830,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>45965</v>
       </c>
@@ -13390,7 +14853,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>45972</v>
       </c>
@@ -13413,7 +14876,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>45979</v>
       </c>
@@ -13436,7 +14899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>45986</v>
       </c>
@@ -13459,7 +14922,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>45993</v>
       </c>
@@ -13482,7 +14945,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>46000</v>
       </c>
@@ -13505,7 +14968,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>46007</v>
       </c>
@@ -13528,7 +14991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>46014</v>
       </c>
@@ -13551,7 +15014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>46021</v>
       </c>
@@ -13574,7 +15037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>46028</v>
       </c>
@@ -13597,7 +15060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46035</v>
       </c>
@@ -13620,7 +15083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46042</v>
       </c>
@@ -13643,7 +15106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46049</v>
       </c>
@@ -13666,7 +15129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46056</v>
       </c>
@@ -13689,7 +15152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46063</v>
       </c>
@@ -13712,7 +15175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46077</v>
       </c>
@@ -13735,7 +15198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46084</v>
       </c>
@@ -13758,7 +15221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46091</v>
       </c>
@@ -13781,7 +15244,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46098</v>
       </c>
@@ -13804,7 +15267,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46105</v>
       </c>
@@ -13827,7 +15290,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46112</v>
       </c>
@@ -13850,7 +15313,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46119</v>
       </c>
@@ -13873,7 +15336,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46126</v>
       </c>
@@ -13896,7 +15359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46133</v>
       </c>
@@ -13919,7 +15382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46140</v>
       </c>
@@ -13942,7 +15405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46147</v>
       </c>
@@ -13965,7 +15428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46154</v>
       </c>
@@ -13988,7 +15451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46161</v>
       </c>
@@ -14011,7 +15474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46168</v>
       </c>
@@ -14034,7 +15497,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46175</v>
       </c>
@@ -14057,7 +15520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46182</v>
       </c>
@@ -14080,7 +15543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46189</v>
       </c>
@@ -14103,7 +15566,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46196</v>
       </c>
@@ -14126,7 +15589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46203</v>
       </c>
@@ -14149,7 +15612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46210</v>
       </c>
@@ -14172,7 +15635,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46217</v>
       </c>
@@ -14195,7 +15658,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46224</v>
       </c>
@@ -14218,7 +15681,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46231</v>
       </c>
@@ -14241,7 +15704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46238</v>
       </c>
@@ -14262,6 +15725,167 @@
       </c>
       <c r="G54" s="16">
         <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="16">
+        <v>21</v>
+      </c>
+      <c r="F55" s="16">
+        <v>24</v>
+      </c>
+      <c r="G55" s="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="16">
+        <v>22.4</v>
+      </c>
+      <c r="F56" s="16">
+        <v>25.4</v>
+      </c>
+      <c r="G56" s="16">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="16">
+        <v>22.4</v>
+      </c>
+      <c r="F57" s="16">
+        <v>25.4</v>
+      </c>
+      <c r="G57" s="16">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="16">
+        <v>22.4</v>
+      </c>
+      <c r="F58" s="16">
+        <v>25.4</v>
+      </c>
+      <c r="G58" s="16">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="16">
+        <v>22.8</v>
+      </c>
+      <c r="F59" s="16">
+        <v>25.8</v>
+      </c>
+      <c r="G59" s="16">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="16">
+        <v>24</v>
+      </c>
+      <c r="F60" s="16">
+        <v>27</v>
+      </c>
+      <c r="G60" s="16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="16">
+        <v>24</v>
+      </c>
+      <c r="F61" s="16">
+        <v>27</v>
+      </c>
+      <c r="G61" s="16">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -14274,7 +15898,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125E0383-8D21-4789-B003-A94DDDB82616}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
